--- a/Hardware Calcs.xlsx
+++ b/Hardware Calcs.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quila\Local_Projects\ECSE\ECSE Design Competition 2\2026-ECSE-Design-Comp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicke\Documents\2026-ECSE-Design-Comp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2B0CDF-B427-4919-8BE9-06537D67253C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755C7818-A529-4539-B030-E96C1B68CB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2_emitter calc" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -98,8 +99,71 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={A5390012-255B-499A-B74E-649FB8BE9920}</author>
+    <author>tc={DA2D2569-F5F0-424C-B2F7-063C719F3896}</author>
+    <author>tc={7349BBD8-4373-4CCC-9547-CD6EDCC81182}</author>
+    <author>tc={9665F46B-9919-4FF1-9A7D-962B15561CAF}</author>
+    <author>tc={10252B12-7C44-45C0-8191-ED9B383798FC}</author>
+    <author>tc={06244395-495E-475E-9A69-7F5A96B98380}</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{A5390012-255B-499A-B74E-649FB8BE9920}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W/sr at 100mA. This is maximum current allowed by emitter.</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="1" shapeId="0" xr:uid="{DA2D2569-F5F0-424C-B2F7-063C719F3896}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Distances in m</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="2" shapeId="0" xr:uid="{7349BBD8-4373-4CCC-9547-CD6EDCC81182}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    A/W</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="3" shapeId="0" xr:uid="{9665F46B-9919-4FF1-9A7D-962B15561CAF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Relative emission brightness of 850nm light.</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="4" shapeId="0" xr:uid="{10252B12-7C44-45C0-8191-ED9B383798FC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Relative sensitivity to 850nm light</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="5" shapeId="0" xr:uid="{06244395-495E-475E-9A69-7F5A96B98380}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    m^2</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>Emitter</t>
   </si>
@@ -150,13 +214,16 @@
   </si>
   <si>
     <t>Emitter Frequency (Hz)</t>
+  </si>
+  <si>
+    <t>Duty Cycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +244,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -203,11 +276,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,35 +589,58 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C4" dT="2026-06-14T00:01:57.93" personId="{5DA4D9E2-D499-4186-A858-7BCB1F916EF6}" id="{A5390012-255B-499A-B74E-649FB8BE9920}">
+    <text>W/sr at 100mA. This is maximum current allowed by emitter.</text>
+  </threadedComment>
+  <threadedComment ref="F4" dT="2026-06-13T23:59:56.83" personId="{5DA4D9E2-D499-4186-A858-7BCB1F916EF6}" id="{DA2D2569-F5F0-424C-B2F7-063C719F3896}">
+    <text>Distances in m</text>
+  </threadedComment>
+  <threadedComment ref="F6" dT="2026-06-13T23:58:25.20" personId="{5DA4D9E2-D499-4186-A858-7BCB1F916EF6}" id="{7349BBD8-4373-4CCC-9547-CD6EDCC81182}">
+    <text>A/W</text>
+  </threadedComment>
+  <threadedComment ref="B7" dT="2026-06-13T23:50:50.31" personId="{5DA4D9E2-D499-4186-A858-7BCB1F916EF6}" id="{9665F46B-9919-4FF1-9A7D-962B15561CAF}">
+    <text>Relative emission brightness of 850nm light.</text>
+  </threadedComment>
+  <threadedComment ref="E7" dT="2026-06-13T23:50:24.84" personId="{5DA4D9E2-D499-4186-A858-7BCB1F916EF6}" id="{10252B12-7C44-45C0-8191-ED9B383798FC}">
+    <text>Relative sensitivity to 850nm light</text>
+  </threadedComment>
+  <threadedComment ref="F8" dT="2026-06-14T00:05:24.32" personId="{5DA4D9E2-D499-4186-A858-7BCB1F916EF6}" id="{06244395-495E-475E-9A69-7F5A96B98380}">
+    <text>m^2</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="I2" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -561,11 +657,11 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
         <v>5</v>
       </c>
@@ -573,7 +669,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>11</v>
       </c>
@@ -581,7 +677,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -596,7 +692,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -612,7 +708,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>8</v>
       </c>
@@ -620,7 +716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -633,11 +729,11 @@
         <v>4.4444444444444447E-5</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>$C$8*C$13</f>
         <v>6.3E-7</v>
       </c>
@@ -646,11 +742,171 @@
         <v>2.52E-6</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
+        <f>C14*$F$7*$F$6</f>
+        <v>3.5154000000000004E-7</v>
+      </c>
+      <c r="D15">
+        <f>D14*$F$7*$F$6</f>
+        <v>1.4061600000000001E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4BF82C-C0F2-4F6F-8968-BBCA72124B8C}">
+  <dimension ref="B2:I15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <f>0.063</f>
+        <v>6.3E-2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>0.15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>0.3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <f>0.9</f>
+        <v>0.9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <f>C4*C7</f>
+        <v>5.67E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <f>1*(10^-3)^2</f>
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <f>$F$8/$F$5^2</f>
+        <v>1.1111111111111112E-5</v>
+      </c>
+      <c r="D13">
+        <f>$F$8/$F$4^2</f>
+        <v>4.4444444444444447E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
+        <f>$C$8*C$13</f>
+        <v>6.3E-7</v>
+      </c>
+      <c r="D14">
+        <f>$C$8*D$13</f>
+        <v>2.52E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
         <f>C14*$F$7*$F$6</f>
         <v>3.5154000000000004E-7</v>
       </c>

--- a/Hardware Calcs.xlsx
+++ b/Hardware Calcs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicke\Documents\2026-ECSE-Design-Comp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quila\Local_Projects\ECSE\ECSE_Design_Competition_2\2026-ECSE-Design-Comp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755C7818-A529-4539-B030-E96C1B68CB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -223,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,12 +244,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -615,18 +609,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.5">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -640,7 +634,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -661,7 +655,7 @@
         <v>38000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E5" t="s">
         <v>5</v>
       </c>
@@ -669,7 +663,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
         <v>11</v>
       </c>
@@ -677,7 +671,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -692,7 +686,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -708,7 +702,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>8</v>
       </c>
@@ -716,7 +710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -729,7 +723,7 @@
         <v>4.4444444444444447E-5</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -742,7 +736,7 @@
         <v>2.52E-6</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -769,18 +763,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4BF82C-C0F2-4F6F-8968-BBCA72124B8C}">
   <dimension ref="B2:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" ht="21" x14ac:dyDescent="0.5">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -794,7 +788,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -815,7 +809,7 @@
         <v>38000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E5" t="s">
         <v>5</v>
       </c>
@@ -829,7 +823,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
         <v>11</v>
       </c>
@@ -837,7 +831,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -852,7 +846,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -868,7 +862,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>8</v>
       </c>
@@ -876,7 +870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -889,7 +883,7 @@
         <v>4.4444444444444447E-5</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -902,7 +896,7 @@
         <v>2.52E-6</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>12</v>
       </c>
